--- a/Results/Bidding/dsfunction_November2025_exact_V5_k20_classified_width.xlsx
+++ b/Results/Bidding/dsfunction_November2025_exact_V5_k20_classified_width.xlsx
@@ -189,8 +189,8 @@
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Hans" typeface="SimSun"/>
+        <a:font script="Hant" typeface="PMingLiU"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -223,8 +223,8 @@
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Hans" typeface="SimSun"/>
+        <a:font script="Hant" typeface="PMingLiU"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
